--- a/database/event/3666/event_3666_evp_summary.xlsx
+++ b/database/event/3666/event_3666_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12.3219</v>
+        <v>12.306</v>
       </c>
       <c r="C2" t="n">
-        <v>4.9725</v>
+        <v>4.9661</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5564</v>
+        <v>4.4588</v>
       </c>
       <c r="E2" t="n">
-        <v>12.3219</v>
+        <v>12.306</v>
       </c>
       <c r="F2" t="n">
-        <v>5.7078</v>
+        <v>5.692</v>
       </c>
       <c r="G2" t="n">
         <v>6.614</v>
       </c>
       <c r="H2" t="n">
-        <v>6.6468</v>
+        <v>6.622</v>
       </c>
       <c r="I2" t="n">
         <v>6.6777</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.139900000000001</v>
+        <v>9.1258</v>
       </c>
       <c r="C3" t="n">
-        <v>3.6884</v>
+        <v>3.6827</v>
       </c>
       <c r="D3" t="n">
-        <v>3.271</v>
+        <v>3.1918</v>
       </c>
       <c r="E3" t="n">
-        <v>9.139900000000001</v>
+        <v>9.1258</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7848</v>
+        <v>3.7707</v>
       </c>
       <c r="G3" t="n">
         <v>5.3551</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7848</v>
+        <v>3.7707</v>
       </c>
       <c r="I3" t="n">
         <v>3.8024</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.4574</v>
+        <v>7.4437</v>
       </c>
       <c r="C4" t="n">
-        <v>3.0095</v>
+        <v>3.0039</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5913</v>
+        <v>2.5217</v>
       </c>
       <c r="E4" t="n">
-        <v>7.4574</v>
+        <v>7.4437</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6684</v>
+        <v>3.6547</v>
       </c>
       <c r="G4" t="n">
         <v>3.789</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6684</v>
+        <v>3.6547</v>
       </c>
       <c r="I4" t="n">
         <v>3.6855</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.0698</v>
+        <v>7.0569</v>
       </c>
       <c r="C5" t="n">
-        <v>2.853</v>
+        <v>2.8478</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4347</v>
+        <v>2.3676</v>
       </c>
       <c r="E5" t="n">
-        <v>7.0698</v>
+        <v>7.0569</v>
       </c>
       <c r="F5" t="n">
-        <v>4.9224</v>
+        <v>4.9095</v>
       </c>
       <c r="G5" t="n">
         <v>2.1474</v>
       </c>
       <c r="H5" t="n">
-        <v>5.4152</v>
+        <v>5.395</v>
       </c>
       <c r="I5" t="n">
         <v>5.4404</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.9573</v>
+        <v>6.9456</v>
       </c>
       <c r="C6" t="n">
-        <v>2.8076</v>
+        <v>2.8029</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3892</v>
+        <v>2.3232</v>
       </c>
       <c r="E6" t="n">
-        <v>6.9573</v>
+        <v>6.9456</v>
       </c>
       <c r="F6" t="n">
-        <v>4.0606</v>
+        <v>4.0489</v>
       </c>
       <c r="G6" t="n">
         <v>2.8967</v>
       </c>
       <c r="H6" t="n">
-        <v>4.064</v>
+        <v>4.0489</v>
       </c>
       <c r="I6" t="n">
         <v>4.0829</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.5633</v>
+        <v>6.5486</v>
       </c>
       <c r="C7" t="n">
-        <v>2.6486</v>
+        <v>2.6427</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2301</v>
+        <v>2.1651</v>
       </c>
       <c r="E7" t="n">
-        <v>6.5633</v>
+        <v>6.5486</v>
       </c>
       <c r="F7" t="n">
-        <v>3.9662</v>
+        <v>3.9515</v>
       </c>
       <c r="G7" t="n">
         <v>2.5971</v>
       </c>
       <c r="H7" t="n">
-        <v>3.9662</v>
+        <v>3.9515</v>
       </c>
       <c r="I7" t="n">
         <v>3.9847</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.9504</v>
+        <v>5.9412</v>
       </c>
       <c r="C8" t="n">
-        <v>2.4013</v>
+        <v>2.3976</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9825</v>
+        <v>1.9231</v>
       </c>
       <c r="E8" t="n">
-        <v>5.9504</v>
+        <v>5.9412</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4682</v>
+        <v>2.459</v>
       </c>
       <c r="G8" t="n">
         <v>3.4822</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4682</v>
+        <v>2.459</v>
       </c>
       <c r="I8" t="n">
         <v>2.4797</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.3461</v>
+        <v>5.3369</v>
       </c>
       <c r="C9" t="n">
-        <v>2.1574</v>
+        <v>2.1537</v>
       </c>
       <c r="D9" t="n">
-        <v>1.7383</v>
+        <v>1.6823</v>
       </c>
       <c r="E9" t="n">
-        <v>5.3461</v>
+        <v>5.3369</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4876</v>
+        <v>2.4783</v>
       </c>
       <c r="G9" t="n">
         <v>2.8586</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4876</v>
+        <v>2.4783</v>
       </c>
       <c r="I9" t="n">
         <v>2.4992</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.961</v>
+        <v>4.9471</v>
       </c>
       <c r="C10" t="n">
-        <v>2.002</v>
+        <v>1.9964</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5828</v>
+        <v>1.527</v>
       </c>
       <c r="E10" t="n">
-        <v>4.961</v>
+        <v>4.9471</v>
       </c>
       <c r="F10" t="n">
-        <v>3.7222</v>
+        <v>3.7083</v>
       </c>
       <c r="G10" t="n">
         <v>1.2388</v>
       </c>
       <c r="H10" t="n">
-        <v>3.7222</v>
+        <v>3.7083</v>
       </c>
       <c r="I10" t="n">
         <v>3.7395</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.917</v>
+        <v>4.9067</v>
       </c>
       <c r="C11" t="n">
-        <v>1.9843</v>
+        <v>1.9801</v>
       </c>
       <c r="D11" t="n">
-        <v>1.565</v>
+        <v>1.5109</v>
       </c>
       <c r="E11" t="n">
-        <v>4.917</v>
+        <v>4.9067</v>
       </c>
       <c r="F11" t="n">
-        <v>4.2321</v>
+        <v>4.2218</v>
       </c>
       <c r="G11" t="n">
         <v>0.6849</v>
       </c>
       <c r="H11" t="n">
-        <v>4.3329</v>
+        <v>4.3167</v>
       </c>
       <c r="I11" t="n">
         <v>4.353</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.772</v>
+        <v>4.7614</v>
       </c>
       <c r="C12" t="n">
-        <v>1.9258</v>
+        <v>1.9215</v>
       </c>
       <c r="D12" t="n">
-        <v>1.5064</v>
+        <v>1.453</v>
       </c>
       <c r="E12" t="n">
-        <v>4.772</v>
+        <v>4.7614</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8652</v>
+        <v>2.8545</v>
       </c>
       <c r="G12" t="n">
         <v>1.9069</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8652</v>
+        <v>2.8545</v>
       </c>
       <c r="I12" t="n">
         <v>2.8785</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.7099</v>
+        <v>4.6988</v>
       </c>
       <c r="C13" t="n">
-        <v>1.9007</v>
+        <v>1.8962</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4813</v>
+        <v>1.4281</v>
       </c>
       <c r="E13" t="n">
-        <v>4.7099</v>
+        <v>4.6988</v>
       </c>
       <c r="F13" t="n">
-        <v>4.4506</v>
+        <v>4.4395</v>
       </c>
       <c r="G13" t="n">
         <v>0.2593</v>
       </c>
       <c r="H13" t="n">
-        <v>4.6755</v>
+        <v>4.6581</v>
       </c>
       <c r="I13" t="n">
         <v>4.6973</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.6747</v>
+        <v>4.6669</v>
       </c>
       <c r="C14" t="n">
-        <v>1.8865</v>
+        <v>1.8833</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4671</v>
+        <v>1.4154</v>
       </c>
       <c r="E14" t="n">
-        <v>4.6747</v>
+        <v>4.6669</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0959</v>
+        <v>2.0881</v>
       </c>
       <c r="G14" t="n">
         <v>2.5788</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0959</v>
+        <v>2.0881</v>
       </c>
       <c r="I14" t="n">
         <v>2.1057</v>
@@ -1090,93 +1090,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.654</v>
+        <v>4.6493</v>
       </c>
       <c r="C15" t="n">
-        <v>1.8781</v>
+        <v>1.8762</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4588</v>
+        <v>1.4084</v>
       </c>
       <c r="E15" t="n">
-        <v>4.654</v>
+        <v>4.6493</v>
       </c>
       <c r="F15" t="n">
-        <v>4.4182</v>
+        <v>4.3544</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2358</v>
+        <v>0.2949</v>
       </c>
       <c r="H15" t="n">
-        <v>4.6247</v>
+        <v>4.5246</v>
       </c>
       <c r="I15" t="n">
-        <v>4.6463</v>
+        <v>4.5246</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2358</v>
+        <v>0.2949</v>
       </c>
       <c r="K15" t="n">
-        <v>276</v>
+        <v>219</v>
       </c>
       <c r="L15" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="M15" t="n">
-        <v>4.8821</v>
+        <v>4.819500000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>346</v>
+        <v>296</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.6493</v>
+        <v>4.643</v>
       </c>
       <c r="C16" t="n">
-        <v>1.8762</v>
+        <v>1.8737</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4569</v>
+        <v>1.4059</v>
       </c>
       <c r="E16" t="n">
-        <v>4.6493</v>
+        <v>4.643</v>
       </c>
       <c r="F16" t="n">
-        <v>4.3544</v>
+        <v>4.4072</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2949</v>
+        <v>0.2358</v>
       </c>
       <c r="H16" t="n">
-        <v>4.5246</v>
+        <v>4.6075</v>
       </c>
       <c r="I16" t="n">
-        <v>4.5246</v>
+        <v>4.6463</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2949</v>
+        <v>0.2358</v>
       </c>
       <c r="K16" t="n">
-        <v>219</v>
+        <v>276</v>
       </c>
       <c r="L16" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="M16" t="n">
-        <v>4.819500000000001</v>
+        <v>4.8821</v>
       </c>
       <c r="N16" t="n">
-        <v>296</v>
+        <v>346</v>
       </c>
     </row>
     <row r="17">
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.6246</v>
+        <v>4.6126</v>
       </c>
       <c r="C17" t="n">
-        <v>1.8663</v>
+        <v>1.8614</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4469</v>
+        <v>1.3938</v>
       </c>
       <c r="E17" t="n">
-        <v>4.6246</v>
+        <v>4.6126</v>
       </c>
       <c r="F17" t="n">
-        <v>4.6909</v>
+        <v>4.6789</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0663</v>
       </c>
       <c r="H17" t="n">
-        <v>5.0523</v>
+        <v>5.0335</v>
       </c>
       <c r="I17" t="n">
         <v>5.0759</v>
@@ -1238,7 +1238,7 @@
         <v>1.772</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3525</v>
+        <v>1.3054</v>
       </c>
       <c r="E18" t="n">
         <v>4.3909</v>
@@ -1284,7 +1284,7 @@
         <v>1.7231</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3036</v>
+        <v>1.2572</v>
       </c>
       <c r="E19" t="n">
         <v>4.2699</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.1901</v>
+        <v>4.1776</v>
       </c>
       <c r="C20" t="n">
-        <v>1.6909</v>
+        <v>1.6859</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2713</v>
+        <v>1.2204</v>
       </c>
       <c r="E20" t="n">
-        <v>4.1901</v>
+        <v>4.1776</v>
       </c>
       <c r="F20" t="n">
-        <v>3.3559</v>
+        <v>3.3434</v>
       </c>
       <c r="G20" t="n">
         <v>0.8342000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>3.3559</v>
+        <v>3.3434</v>
       </c>
       <c r="I20" t="n">
         <v>3.3716</v>
@@ -1376,7 +1376,7 @@
         <v>1.6528</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2332</v>
+        <v>1.1878</v>
       </c>
       <c r="E21" t="n">
         <v>4.0956</v>
@@ -1422,7 +1422,7 @@
         <v>1.4833</v>
       </c>
       <c r="D22" t="n">
-        <v>1.0635</v>
+        <v>1.0204</v>
       </c>
       <c r="E22" t="n">
         <v>3.6755</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.5421</v>
+        <v>3.5303</v>
       </c>
       <c r="C23" t="n">
-        <v>1.4294</v>
+        <v>1.4247</v>
       </c>
       <c r="D23" t="n">
-        <v>1.0096</v>
+        <v>0.9626</v>
       </c>
       <c r="E23" t="n">
-        <v>3.5421</v>
+        <v>3.5303</v>
       </c>
       <c r="F23" t="n">
-        <v>3.1755</v>
+        <v>3.1637</v>
       </c>
       <c r="G23" t="n">
         <v>0.3666</v>
       </c>
       <c r="H23" t="n">
-        <v>3.1755</v>
+        <v>3.1637</v>
       </c>
       <c r="I23" t="n">
         <v>3.1903</v>
@@ -1514,7 +1514,7 @@
         <v>1.3125</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8925</v>
+        <v>0.8518</v>
       </c>
       <c r="E24" t="n">
         <v>3.2524</v>
@@ -1560,7 +1560,7 @@
         <v>1.2231</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8031</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="E25" t="n">
         <v>3.0309</v>
@@ -1606,7 +1606,7 @@
         <v>1.1694</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7493</v>
+        <v>0.7106</v>
       </c>
       <c r="E26" t="n">
         <v>2.8978</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.8339</v>
+        <v>2.833</v>
       </c>
       <c r="C27" t="n">
-        <v>1.1436</v>
+        <v>1.1433</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7235</v>
+        <v>0.6848</v>
       </c>
       <c r="E27" t="n">
-        <v>2.8339</v>
+        <v>2.833</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2306</v>
+        <v>0.2298</v>
       </c>
       <c r="G27" t="n">
         <v>2.6032</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2306</v>
+        <v>0.2298</v>
       </c>
       <c r="I27" t="n">
         <v>0.2317</v>
@@ -1698,7 +1698,7 @@
         <v>0.9922</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5719</v>
+        <v>0.5356</v>
       </c>
       <c r="E28" t="n">
         <v>2.4587</v>
@@ -1744,7 +1744,7 @@
         <v>0.8996</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4792</v>
+        <v>0.4442</v>
       </c>
       <c r="E29" t="n">
         <v>2.2292</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.1591</v>
+        <v>2.1513</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8713</v>
+        <v>0.8682</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4509</v>
+        <v>0.4132</v>
       </c>
       <c r="E30" t="n">
-        <v>2.1591</v>
+        <v>2.1513</v>
       </c>
       <c r="F30" t="n">
-        <v>2.0809</v>
+        <v>2.0731</v>
       </c>
       <c r="G30" t="n">
         <v>0.07820000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>2.0809</v>
+        <v>2.0731</v>
       </c>
       <c r="I30" t="n">
         <v>2.0906</v>
@@ -1836,7 +1836,7 @@
         <v>0.8142</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3937</v>
+        <v>0.3599</v>
       </c>
       <c r="E31" t="n">
         <v>2.0175</v>
@@ -1882,7 +1882,7 @@
         <v>0.7872</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3666</v>
+        <v>0.3332</v>
       </c>
       <c r="E32" t="n">
         <v>1.9506</v>
@@ -1928,7 +1928,7 @@
         <v>0.7716</v>
       </c>
       <c r="D33" t="n">
-        <v>0.351</v>
+        <v>0.3178</v>
       </c>
       <c r="E33" t="n">
         <v>1.912</v>
@@ -1974,7 +1974,7 @@
         <v>0.717</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2963</v>
+        <v>0.2639</v>
       </c>
       <c r="E34" t="n">
         <v>1.7766</v>
@@ -2020,7 +2020,7 @@
         <v>0.6423</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2216</v>
+        <v>0.1902</v>
       </c>
       <c r="E35" t="n">
         <v>1.5917</v>
@@ -2066,7 +2066,7 @@
         <v>0.5926</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1719</v>
+        <v>0.1411</v>
       </c>
       <c r="E36" t="n">
         <v>1.4685</v>
@@ -2112,7 +2112,7 @@
         <v>0.5172</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0964</v>
+        <v>0.0667</v>
       </c>
       <c r="E37" t="n">
         <v>1.2816</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.2593</v>
+        <v>1.252</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5082</v>
+        <v>0.5052</v>
       </c>
       <c r="D38" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0549</v>
       </c>
       <c r="E38" t="n">
-        <v>1.2593</v>
+        <v>1.252</v>
       </c>
       <c r="F38" t="n">
-        <v>1.9593</v>
+        <v>1.952</v>
       </c>
       <c r="G38" t="n">
         <v>-0.7</v>
       </c>
       <c r="H38" t="n">
-        <v>1.9593</v>
+        <v>1.952</v>
       </c>
       <c r="I38" t="n">
         <v>1.9684</v>
@@ -2204,7 +2204,7 @@
         <v>0.4955</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0746</v>
+        <v>0.0452</v>
       </c>
       <c r="E39" t="n">
         <v>1.2278</v>
@@ -2250,7 +2250,7 @@
         <v>0.4885</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0677</v>
+        <v>0.0384</v>
       </c>
       <c r="E40" t="n">
         <v>1.2105</v>
@@ -2296,7 +2296,7 @@
         <v>0.4822</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0614</v>
+        <v>0.0322</v>
       </c>
       <c r="E41" t="n">
         <v>1.195</v>
@@ -2342,7 +2342,7 @@
         <v>0.477</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0561</v>
+        <v>0.027</v>
       </c>
       <c r="E42" t="n">
         <v>1.1819</v>
@@ -2388,7 +2388,7 @@
         <v>0.4093</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.0116</v>
+        <v>-0.0398</v>
       </c>
       <c r="E43" t="n">
         <v>1.0143</v>
@@ -2434,7 +2434,7 @@
         <v>0.3825</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.0385</v>
+        <v>-0.0663</v>
       </c>
       <c r="E44" t="n">
         <v>0.9478</v>
@@ -2480,7 +2480,7 @@
         <v>0.3506</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.0704</v>
+        <v>-0.0978</v>
       </c>
       <c r="E45" t="n">
         <v>0.8688</v>
@@ -2526,7 +2526,7 @@
         <v>0.3373</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.0837</v>
+        <v>-0.1109</v>
       </c>
       <c r="E46" t="n">
         <v>0.8359</v>
@@ -2572,7 +2572,7 @@
         <v>0.2508</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.1703</v>
+        <v>-0.1963</v>
       </c>
       <c r="E47" t="n">
         <v>0.6215000000000001</v>
@@ -2618,7 +2618,7 @@
         <v>0.2387</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.1824</v>
+        <v>-0.2083</v>
       </c>
       <c r="E48" t="n">
         <v>0.5915</v>
@@ -2664,7 +2664,7 @@
         <v>0.1928</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.2284</v>
+        <v>-0.2536</v>
       </c>
       <c r="E49" t="n">
         <v>0.4777</v>
@@ -2710,7 +2710,7 @@
         <v>0.1825</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.2386</v>
+        <v>-0.2637</v>
       </c>
       <c r="E50" t="n">
         <v>0.4523</v>
@@ -2756,7 +2756,7 @@
         <v>0.1364</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.2849</v>
+        <v>-0.3093</v>
       </c>
       <c r="E51" t="n">
         <v>0.3379</v>
@@ -2802,7 +2802,7 @@
         <v>0.1303</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.291</v>
+        <v>-0.3153</v>
       </c>
       <c r="E52" t="n">
         <v>0.3228</v>
@@ -2848,7 +2848,7 @@
         <v>0.0819</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.3394</v>
+        <v>-0.3631</v>
       </c>
       <c r="E53" t="n">
         <v>0.2029</v>
@@ -2894,7 +2894,7 @@
         <v>0.0594</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.3619</v>
+        <v>-0.3853</v>
       </c>
       <c r="E54" t="n">
         <v>0.1471</v>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.0887</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0374</v>
+        <v>0.0358</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.3839</v>
+        <v>-0.4086</v>
       </c>
       <c r="E55" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.0887</v>
       </c>
       <c r="F55" t="n">
-        <v>1.0928</v>
+        <v>1.0887</v>
       </c>
       <c r="G55" t="n">
         <v>-1</v>
       </c>
       <c r="H55" t="n">
-        <v>1.0928</v>
+        <v>1.0887</v>
       </c>
       <c r="I55" t="n">
         <v>1.0979</v>
@@ -2986,7 +2986,7 @@
         <v>0.0169</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4044</v>
+        <v>-0.4272</v>
       </c>
       <c r="E56" t="n">
         <v>0.042</v>
@@ -3032,7 +3032,7 @@
         <v>0.0126</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.4088</v>
+        <v>-0.4315</v>
       </c>
       <c r="E57" t="n">
         <v>0.0312</v>
@@ -3078,7 +3078,7 @@
         <v>-0.001</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.4224</v>
+        <v>-0.4449</v>
       </c>
       <c r="E58" t="n">
         <v>-0.0025</v>
@@ -3124,7 +3124,7 @@
         <v>-0.1027</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5242</v>
+        <v>-0.5453</v>
       </c>
       <c r="E59" t="n">
         <v>-0.2545</v>
@@ -3170,7 +3170,7 @@
         <v>-0.1312</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5527</v>
+        <v>-0.5735</v>
       </c>
       <c r="E60" t="n">
         <v>-0.3252</v>
@@ -3216,7 +3216,7 @@
         <v>-0.188</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6096</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="E61" t="n">
         <v>-0.4659</v>
@@ -3262,7 +3262,7 @@
         <v>-0.2149</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6365</v>
+        <v>-0.6561</v>
       </c>
       <c r="E62" t="n">
         <v>-0.5326</v>
@@ -3308,7 +3308,7 @@
         <v>-0.2649</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6865</v>
+        <v>-0.7054</v>
       </c>
       <c r="E63" t="n">
         <v>-0.6563</v>
@@ -3354,7 +3354,7 @@
         <v>-0.2845</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7062</v>
+        <v>-0.7248</v>
       </c>
       <c r="E64" t="n">
         <v>-0.7050999999999999</v>
@@ -3400,7 +3400,7 @@
         <v>-0.3481</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7698</v>
+        <v>-0.7876</v>
       </c>
       <c r="E65" t="n">
         <v>-0.8626</v>
@@ -3446,7 +3446,7 @@
         <v>-0.3495</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7712</v>
+        <v>-0.7889</v>
       </c>
       <c r="E66" t="n">
         <v>-0.866</v>
@@ -3492,7 +3492,7 @@
         <v>-0.3667</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7885</v>
+        <v>-0.806</v>
       </c>
       <c r="E67" t="n">
         <v>-0.9088000000000001</v>
@@ -3538,7 +3538,7 @@
         <v>-0.4131</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8349</v>
+        <v>-0.8518</v>
       </c>
       <c r="E68" t="n">
         <v>-1.0237</v>
@@ -3584,7 +3584,7 @@
         <v>-0.4232</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.845</v>
+        <v>-0.8617</v>
       </c>
       <c r="E69" t="n">
         <v>-1.0487</v>
@@ -3624,25 +3624,25 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.0891</v>
+        <v>-1.0898</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.4395</v>
+        <v>-0.4398</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8613</v>
+        <v>-0.8781</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.0891</v>
+        <v>-1.0898</v>
       </c>
       <c r="F70" t="n">
-        <v>0.1805</v>
+        <v>0.1798</v>
       </c>
       <c r="G70" t="n">
         <v>-1.2696</v>
       </c>
       <c r="H70" t="n">
-        <v>0.1805</v>
+        <v>0.1798</v>
       </c>
       <c r="I70" t="n">
         <v>0.1813</v>
@@ -3676,7 +3676,7 @@
         <v>-0.4533</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8751</v>
+        <v>-0.8914</v>
       </c>
       <c r="E71" t="n">
         <v>-1.1232</v>
@@ -3722,7 +3722,7 @@
         <v>-0.732</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.1541</v>
+        <v>-1.1666</v>
       </c>
       <c r="E72" t="n">
         <v>-1.8139</v>
@@ -3768,7 +3768,7 @@
         <v>-0.8105</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.2327</v>
+        <v>-1.244</v>
       </c>
       <c r="E73" t="n">
         <v>-2.0083</v>
@@ -3814,7 +3814,7 @@
         <v>-0.8226</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.2448</v>
+        <v>-1.256</v>
       </c>
       <c r="E74" t="n">
         <v>-2.0383</v>
@@ -3860,7 +3860,7 @@
         <v>-0.9444</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.3668</v>
+        <v>-1.3762</v>
       </c>
       <c r="E75" t="n">
         <v>-2.3402</v>
@@ -3906,7 +3906,7 @@
         <v>-1.0547</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.4772</v>
+        <v>-1.4852</v>
       </c>
       <c r="E76" t="n">
         <v>-2.6136</v>
@@ -3946,25 +3946,25 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-2.9141</v>
+        <v>-2.9107</v>
       </c>
       <c r="C77" t="n">
-        <v>-1.176</v>
+        <v>-1.1746</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.5986</v>
+        <v>-1.6035</v>
       </c>
       <c r="E77" t="n">
-        <v>-2.9141</v>
+        <v>-2.9107</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.9141</v>
+        <v>-0.9107</v>
       </c>
       <c r="G77" t="n">
         <v>-2</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.9141</v>
+        <v>-0.9107</v>
       </c>
       <c r="I77" t="n">
         <v>-0.9184</v>
@@ -3998,7 +3998,7 @@
         <v>-1.3255</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.7483</v>
+        <v>-1.7525</v>
       </c>
       <c r="E78" t="n">
         <v>-3.2847</v>
@@ -4044,7 +4044,7 @@
         <v>-1.4082</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.831</v>
+        <v>-1.8341</v>
       </c>
       <c r="E79" t="n">
         <v>-3.4895</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-3.7196</v>
+        <v>-3.7091</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.5011</v>
+        <v>-1.4968</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.924</v>
+        <v>-1.9216</v>
       </c>
       <c r="E80" t="n">
-        <v>-3.7196</v>
+        <v>-3.7091</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.812</v>
+        <v>-2.8015</v>
       </c>
       <c r="G80" t="n">
         <v>-0.9076</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.812</v>
+        <v>-2.8015</v>
       </c>
       <c r="I80" t="n">
         <v>-2.8251</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.929</v>
+        <v>-3.9187</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.5856</v>
+        <v>-1.5814</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.0086</v>
+        <v>-2.0051</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.929</v>
+        <v>-3.9187</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.7514</v>
+        <v>-2.7411</v>
       </c>
       <c r="G81" t="n">
         <v>-1.1776</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.7514</v>
+        <v>-2.7411</v>
       </c>
       <c r="I81" t="n">
         <v>-2.7642</v>
